--- a/output/roomself_excel/5901.xlsx
+++ b/output/roomself_excel/5901.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>272560</v>
+        <v>122544</v>
       </c>
       <c r="D2" t="n">
-        <v>6106</v>
+        <v>3141</v>
       </c>
       <c r="E2" t="n">
-        <v>822</v>
+        <v>549</v>
       </c>
       <c r="F2" t="n">
-        <v>814</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122544</v>
+        <v>77673</v>
       </c>
       <c r="D3" t="n">
-        <v>3141</v>
+        <v>2875</v>
       </c>
       <c r="E3" t="n">
-        <v>549</v>
+        <v>453</v>
       </c>
       <c r="F3" t="n">
-        <v>335</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77673</v>
+        <v>35323</v>
       </c>
       <c r="D4" t="n">
-        <v>2875</v>
+        <v>1556</v>
       </c>
       <c r="E4" t="n">
-        <v>453</v>
+        <v>226</v>
       </c>
       <c r="F4" t="n">
-        <v>354</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -546,6 +546,28 @@
       </c>
       <c r="F5" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>237237</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5338</v>
+      </c>
+      <c r="E6" t="n">
+        <v>822</v>
+      </c>
+      <c r="F6" t="n">
+        <v>814</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5901.xlsx
+++ b/output/roomself_excel/5901.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,107 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_7</t>
         </is>
       </c>
     </row>
@@ -475,12 +570,59 @@
       <c r="D2" t="n">
         <v>3141</v>
       </c>
-      <c r="E2" t="n">
-        <v>549</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>335</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>317</v>
+      </c>
+      <c r="M2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>313</v>
+      </c>
+      <c r="P2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +639,67 @@
       <c r="D3" t="n">
         <v>2875</v>
       </c>
-      <c r="E3" t="n">
-        <v>453</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>354</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>197</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>185</v>
+      </c>
+      <c r="M3" t="n">
+        <v>29</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>382</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +716,35 @@
       <c r="D4" t="n">
         <v>1556</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>226</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>22</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +761,35 @@
       <c r="D5" t="n">
         <v>1172</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>143</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>22</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +806,82 @@
       <c r="D6" t="n">
         <v>5338</v>
       </c>
-      <c r="E6" t="n">
-        <v>822</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>814</v>
+        <v>132</v>
+      </c>
+      <c r="G6" t="n">
+        <v>51</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>337</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>235</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>135</v>
+      </c>
+      <c r="P6" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>83</v>
+      </c>
+      <c r="S6" t="n">
+        <v>51</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>164</v>
+      </c>
+      <c r="V6" t="n">
+        <v>50</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5901.xlsx
+++ b/output/roomself_excel/5901.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:BE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,166 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_7</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_7</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_7</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_7</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_8</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_8</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_8</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_8</t>
         </is>
       </c>
     </row>
@@ -623,6 +783,74 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>73</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -700,6 +928,38 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -745,6 +1005,50 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>98</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -790,6 +1094,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -882,6 +1218,134 @@
       </c>
       <c r="Y6" t="n">
         <v>30</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
